--- a/LubanConfig/Moba/Production/Datas/J-技能表现表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-技能表现表.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,42 @@
           <t>UsePointMode</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>LockProjectileRadius</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>FanAngleDegrees</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>FanRadius</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>LockOnDurationMs</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>DashDistance</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>SectorAngleDegrees</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>OmittedFields</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>NullFields</t>
         </is>
@@ -606,12 +636,42 @@
           <t>SkillUsePointMode</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -688,12 +748,42 @@
           <t>使用点位模式；按 SkillUsePointMode 枚举或 bean 定义填写。</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>??????????????</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>????????????</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>????????</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>??????????????</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>????????????</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>????????????</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>迁移兼容字段：逗号分隔的原 JSON 缺失字段名；新数据通常留空。</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="V3" s="3" t="inlineStr">
         <is>
           <t>迁移兼容字段：逗号分隔的原 JSON 显式 null 字段名；新数据通常留空。</t>
         </is>
@@ -740,12 +830,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>IndicatorShape,IndicatorWorldWidth,SelfRadius</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n"/>
+      <c r="V4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -794,12 +884,12 @@
           <t>Aim</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n"/>
+      <c r="V5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -848,12 +938,12 @@
           <t>Aim</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P6" s="2" t="n"/>
+      <c r="V6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -902,12 +992,12 @@
           <t>TargetPoint</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P7" s="2" t="n"/>
+      <c r="V7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -956,12 +1046,12 @@
           <t>TargetPoint</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P8" s="2" t="n"/>
+      <c r="V8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1010,12 +1100,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>IndicatorWorldWidth</t>
         </is>
       </c>
-      <c r="P9" s="2" t="n"/>
+      <c r="V9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1064,12 +1154,12 @@
           <t>Aim</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P10" s="2" t="n"/>
+      <c r="V10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1116,12 +1206,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>IndicatorWorldWidth,SelfRadius</t>
         </is>
       </c>
-      <c r="P11" s="2" t="n"/>
+      <c r="V11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1170,12 +1260,12 @@
           <t>Aim</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P12" s="2" t="n"/>
+      <c r="V12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1224,12 +1314,692 @@
           <t>TargetPoint</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>SelfRadius</t>
         </is>
       </c>
-      <c r="P13" s="2" t="n"/>
+      <c r="V13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+      <c r="B14" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>DashLine</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>sun_shangxiang_roll_dash</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" s="2" t="n"/>
+      <c r="V14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>TargetCircle</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>sun_shangxiang_grenade_area</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>TargetPoint</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="n"/>
+      <c r="V15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>DirectionLine</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>sun_shangxiang_cannon_line</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n"/>
+      <c r="V16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>TargetCircle</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>luban_grenade_area</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>TargetPoint</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>DirectionLine</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>luban_shark_cannon_line</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="n"/>
+      <c r="V18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>DirectionArea</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>luban_air_support_target_area</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="n"/>
+      <c r="V19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>LockProjectile</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>daji_charm_lock_on</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1500</v>
+      </c>
+      <c r="U20" s="2" t="n"/>
+      <c r="V20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>SelfCircle</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>daji_ultimate_auto_target_range</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="n"/>
+      <c r="V21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>DashLine</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>mozi_peace_walker_dash</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="n"/>
+      <c r="V22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>SelfCircle</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>mozi_ink_guard_self_area</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="n"/>
+      <c r="V23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>SelfCircle</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>xiaoqiao_starfall_self_area</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="n"/>
+      <c r="V24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>DashLine</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>lianpo_bursting_charge_dash</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Aim</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="U25" s="2" t="n"/>
+      <c r="V25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+      <c r="B26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>SelfCircle</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>lianpo_lava_strike_self_area</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="n"/>
+      <c r="V26" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/LubanConfig/Moba/Production/Datas/J-技能表现表.xlsx
+++ b/LubanConfig/Moba/Production/Datas/J-技能表现表.xlsx
@@ -1448,7 +1448,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>DirectionLine</t>
+          <t>LockProjectile</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
